--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A80CCC7-3B9C-4142-8EC4-636888050998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8501919B-42D2-4F62-94EC-511FBF0A9038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="660" windowWidth="36060" windowHeight="19710" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2070" yWindow="2115" windowWidth="36330" windowHeight="19485" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="327">
   <si>
     <t>Home</t>
   </si>
@@ -1308,18 +1308,9 @@
     <t>Total data quality score</t>
   </si>
   <si>
-    <t>Milk sold</t>
-  </si>
-  <si>
-    <t>Percent income from milk sold</t>
-  </si>
-  <si>
     <t>Dairy cattle</t>
   </si>
   <si>
-    <t>Production and manure management systems</t>
-  </si>
-  <si>
     <t>User friendly description</t>
   </si>
   <si>
@@ -1336,9 +1327,6 @@
   </si>
   <si>
     <t>Geographically generic database</t>
-  </si>
-  <si>
-    <t>Use of contractors and service providers</t>
   </si>
   <si>
     <t>10.1.1-2 Solid waste treatment</t>
@@ -3577,7 +3565,7 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3619,7 +3607,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -15447,7 +15435,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{84D8E3C0-97CA-4CF1-A63F-3CF6AAE07330}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{E41B3FA3-55C1-4BBF-A477-D8EDBC89025E}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="41"/>
     <tableColumn id="3" xr3:uid="{48DB24D2-2F89-4EEB-911F-2F24089C3918}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{879FC871-5C62-44BF-952F-ACBA1C3B6AE4}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{B8588D76-BACA-4516-8963-B7E8E5A87B93}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -15714,8 +15702,8 @@
     <tableColumn id="2" xr3:uid="{7FC986B7-3E05-4518-A4BD-B7EBD33A8B15}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{16526B22-D217-46EF-BC4C-E637FCE5EC95}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{3AAC4A98-CAAD-40B5-A722-73508C5FB166}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{C448A810-BAE3-4F91-9F24-21BAF52A973C}" name="Notes" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{862E9D6B-BB43-41BE-8C67-1D64A642D7F3}" name="Evidence files" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{C448A810-BAE3-4F91-9F24-21BAF52A973C}" name="Notes" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{862E9D6B-BB43-41BE-8C67-1D64A642D7F3}" name="Evidence files" dataDxfId="54"/>
     <tableColumn id="7" xr3:uid="{A9957D63-1EBA-4D14-BC67-2A0E3AA2B419}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15750,8 +15738,8 @@
     <tableColumn id="2" xr3:uid="{D4CB6C67-0558-4F8C-A55A-4C433B91BCE6}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{6E2A6B06-3DDD-4A3D-B134-9424CA31C644}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{FEA1703D-1911-4DEC-82D3-85178A1D42E0}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{3337BFD3-3DF4-4A5A-A926-E755139A6157}" name="Notes" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{12BBF343-9185-4858-889C-52CA6187F028}" name="Evidence files" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{3337BFD3-3DF4-4A5A-A926-E755139A6157}" name="Notes" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{12BBF343-9185-4858-889C-52CA6187F028}" name="Evidence files" dataDxfId="52"/>
     <tableColumn id="7" xr3:uid="{17DE9946-3E3E-4EC2-B523-EF7923BDEA6F}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15768,8 +15756,8 @@
     <tableColumn id="2" xr3:uid="{C56260A7-FB13-4B26-8678-AAA427DA7FC6}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{2D8817D3-070C-4235-B959-84550EDF61B3}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{125CD8F4-EF3A-4071-B192-6795409946D8}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{8A74E42F-C35B-4BDD-9245-839C1F3C1520}" name="Notes" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{3AB4A9DC-680B-447C-8E99-9AB65396E5A9}" name="Evidence files" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{8A74E42F-C35B-4BDD-9245-839C1F3C1520}" name="Notes" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{3AB4A9DC-680B-447C-8E99-9AB65396E5A9}" name="Evidence files" dataDxfId="50"/>
     <tableColumn id="7" xr3:uid="{787C62E0-A9BD-475F-BB50-10FFADB8EB15}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15786,8 +15774,8 @@
     <tableColumn id="2" xr3:uid="{2FFB4163-E47F-407D-B4D6-9583863507A0}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{C7B0DDB8-1A90-4AB7-90CC-6CB1635601DC}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{1A709C61-EFE5-4D80-AA71-A79AC4D162FC}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{7212BD6B-35BD-42D8-9F09-AB4A9E21E11E}" name="Notes" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{ED8DEFB0-F672-4B94-8A8A-08E95B94F452}" name="Evidence files" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{7212BD6B-35BD-42D8-9F09-AB4A9E21E11E}" name="Notes" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{ED8DEFB0-F672-4B94-8A8A-08E95B94F452}" name="Evidence files" dataDxfId="48"/>
     <tableColumn id="7" xr3:uid="{EAC77EB9-8A0A-47A3-953F-56CA1EDD9E53}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15804,8 +15792,8 @@
     <tableColumn id="2" xr3:uid="{95B12875-4F57-460D-AE75-4103EF22C913}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{0703985D-E427-4374-B543-83D0FAAE6508}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{F3E44A87-7F7D-45F0-9B3D-595F89897070}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{BB0AB219-76C5-4C07-8464-6A099FB6C087}" name="Notes" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{55811535-8D98-416A-8E25-DF480443738D}" name="Evidence files" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{BB0AB219-76C5-4C07-8464-6A099FB6C087}" name="Notes" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{55811535-8D98-416A-8E25-DF480443738D}" name="Evidence files" dataDxfId="46"/>
     <tableColumn id="7" xr3:uid="{8413E0FF-2043-42EC-A1B4-A58F9779C482}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15822,8 +15810,8 @@
     <tableColumn id="2" xr3:uid="{52B081B7-B268-4C29-BBBD-2ABFDFCC78C6}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{7C9ED2CA-1AB5-4318-AE1E-18BB67F2312F}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{85CB9257-FE0E-414E-9925-9D7DF17DA6DB}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{8C5D46E1-460B-4C34-B936-B7340702FC8A}" name="Notes" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{6B183878-5EA9-4AA1-88D9-695C68CB6713}" name="Evidence files" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{8C5D46E1-460B-4C34-B936-B7340702FC8A}" name="Notes" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{6B183878-5EA9-4AA1-88D9-695C68CB6713}" name="Evidence files" dataDxfId="44"/>
     <tableColumn id="7" xr3:uid="{59AFF1C5-72B9-4397-97DE-85D9ECCFD14B}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -15840,8 +15828,8 @@
     <tableColumn id="2" xr3:uid="{2D4AFB44-5300-46F3-9156-D8EDC1DE265E}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{A1D0BD11-9716-43AD-83B6-98340DEC6B6C}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{810B210E-D3DD-4C2B-B6F7-D7658FAC417A}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{CF709830-6D5F-4365-B6EA-2DD643D1C7D9}" name="Notes" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{F475BD73-7F40-4FD8-8570-BB188E6B27D1}" name="Evidence files" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{CF709830-6D5F-4365-B6EA-2DD643D1C7D9}" name="Notes" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{F475BD73-7F40-4FD8-8570-BB188E6B27D1}" name="Evidence files" dataDxfId="42"/>
     <tableColumn id="7" xr3:uid="{3CC20754-630A-403A-A4B8-AE12D211F244}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -16887,7 +16875,7 @@
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E32" s="1" t="e" cm="1">
         <f t="array" ref="E32">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Value_Method1</f>
@@ -16915,7 +16903,7 @@
     </row>
     <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E33" s="1" t="e" cm="1">
         <f t="array" ref="E33">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend2_Value_Method1</f>
@@ -16943,7 +16931,7 @@
     </row>
     <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E34" s="1" t="e" cm="1">
         <f t="array" ref="E34">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend3_Value_Method1</f>
@@ -16971,7 +16959,7 @@
     </row>
     <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E35" s="1" t="e" cm="1">
         <f t="array" ref="E35">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend4_Value_Method1</f>
@@ -16999,7 +16987,7 @@
     </row>
     <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E36" s="1" t="e" cm="1">
         <f t="array" ref="E36">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Value_Method1</f>
@@ -17027,7 +17015,7 @@
     </row>
     <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E37" s="1" t="e" cm="1">
         <f t="array" ref="E37">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Value_Method1</f>
@@ -17055,7 +17043,7 @@
     </row>
     <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E38" s="1" t="e" cm="1">
         <f t="array" ref="E38">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Value_Method1</f>
@@ -17083,7 +17071,7 @@
     </row>
     <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E39" s="1" t="e" cm="1">
         <f t="array" ref="E39">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Value_Method1</f>
@@ -17111,7 +17099,7 @@
     </row>
     <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E40" s="1" t="e" cm="1">
         <f t="array" ref="E40">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Value_Method1</f>
@@ -17139,7 +17127,7 @@
     </row>
     <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E41" s="1" t="e" cm="1">
         <f t="array" ref="E41">VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Value_Method1</f>
@@ -17167,7 +17155,7 @@
     </row>
     <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E42" s="1" t="e" cm="1">
         <f t="array" ref="E42">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope1_Result_Method1</f>
@@ -26208,8 +26196,9 @@
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
-        <v>181</v>
+      <c r="D8" s="1" t="str">
+        <f>"Milk produced"</f>
+        <v>Milk produced</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
@@ -26222,8 +26211,9 @@
       </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D9" s="1" t="s">
-        <v>309</v>
+      <c r="D9" s="1" t="str">
+        <f>"Milk sold"</f>
+        <v>Milk sold</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -26299,8 +26289,9 @@
       </c>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="1" t="s">
-        <v>310</v>
+      <c r="D13" s="1" t="str">
+        <f>"Percent income from milk sold"</f>
+        <v>Percent income from milk sold</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
@@ -26522,7 +26513,7 @@
     </row>
     <row r="29" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="4:10" x14ac:dyDescent="0.25">
@@ -26675,8 +26666,9 @@
       </c>
     </row>
     <row r="38" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D38" s="1" t="s">
-        <v>312</v>
+      <c r="D38" s="1" t="str">
+        <f>"Production and manure management systems"</f>
+        <v>Production and manure management systems</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>288</v>
@@ -27209,8 +27201,9 @@
       </c>
     </row>
     <row r="78" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D78" s="1" t="s">
-        <v>319</v>
+      <c r="D78" s="1" t="str">
+        <f>"Use of contractors and service providers"</f>
+        <v>Use of contractors and service providers</v>
       </c>
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
@@ -31417,7 +31410,7 @@
     </row>
     <row r="265" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D265" s="20" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E265" s="20" t="s">
         <v>196</v>
@@ -31518,7 +31511,7 @@
     </row>
     <row r="274" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D274" s="20" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E274" s="20" t="s">
         <v>196</v>
@@ -31619,7 +31612,7 @@
     </row>
     <row r="283" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D283" s="20" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E283" s="20" t="s">
         <v>196</v>
@@ -31720,7 +31713,7 @@
     </row>
     <row r="292" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D292" s="20" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E292" s="20" t="s">
         <v>196</v>
@@ -31736,7 +31729,7 @@
     </row>
     <row r="293" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D293" s="20" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E293" s="20" t="s">
         <v>228</v>
@@ -31752,7 +31745,7 @@
     </row>
     <row r="294" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D294" s="20" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E294" s="20" t="s">
         <v>230</v>
@@ -31768,7 +31761,7 @@
     </row>
     <row r="295" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D295" s="20" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E295" s="20" t="s">
         <v>232</v>
@@ -31784,7 +31777,7 @@
     </row>
     <row r="296" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D296" s="20" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E296" s="20" t="s">
         <v>234</v>
@@ -31800,7 +31793,7 @@
     </row>
     <row r="297" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D297" s="20" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E297" s="20" t="s">
         <v>236</v>
@@ -31844,30 +31837,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -32062,34 +32031,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32106,4 +32072,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>